--- a/Data/CSV/regon.xlsx
+++ b/Data/CSV/regon.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Pulpit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Documents\GitHub\MobilityPatterns\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD4D93B1-42D1-4BFB-8382-B2AECE2BAE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C61015-327A-4837-AFB8-50DCF48EC0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{178E5E3B-8F57-4D60-BDFA-D04E6B9AA60C}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">podregion M. POZNAŃ               </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>powiat M. POZNAŃ</t>
   </si>
@@ -424,23 +421,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -456,6 +438,45 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -467,48 +488,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,234 +823,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401DBD47-1B97-4A32-92C7-8196E923716B}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="14"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="22"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="H2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="19"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="15"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="16" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="V3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="17" t="s">
+      <c r="W3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="X3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="X3" s="17" t="s">
+      <c r="Y3" s="17" t="s">
         <v>16</v>
-      </c>
-      <c r="Y3" s="20" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="20"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="17"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="20"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="17"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="25"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="1">
@@ -1148,546 +1127,488 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="6">
-        <v>136751</v>
-      </c>
-      <c r="C8" s="7">
-        <v>132944</v>
-      </c>
-      <c r="D8" s="7">
-        <v>3074</v>
-      </c>
-      <c r="E8" s="7">
-        <v>589</v>
-      </c>
-      <c r="F8" s="7">
-        <v>116</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="B8" s="1">
+        <v>2433</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2344</v>
+      </c>
+      <c r="D8" s="2">
+        <v>71</v>
+      </c>
+      <c r="E8" s="2">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1999</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1910</v>
+      </c>
+      <c r="P8" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>17</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>18</v>
+      </c>
+      <c r="U8" s="2">
+        <v>18</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
+        <v>30754</v>
+      </c>
+      <c r="C9" s="2">
+        <v>29862</v>
+      </c>
+      <c r="D9" s="2">
+        <v>727</v>
+      </c>
+      <c r="E9" s="2">
+        <v>132</v>
+      </c>
+      <c r="F9" s="2">
         <v>28</v>
       </c>
-      <c r="H8" s="6">
-        <v>1376</v>
-      </c>
-      <c r="I8" s="7">
-        <v>910</v>
-      </c>
-      <c r="J8" s="7">
-        <v>231</v>
-      </c>
-      <c r="K8" s="7">
-        <v>178</v>
-      </c>
-      <c r="L8" s="7">
+      <c r="G9" s="3">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>205</v>
+      </c>
+      <c r="I9" s="2">
+        <v>110</v>
+      </c>
+      <c r="J9" s="2">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2">
+        <v>33</v>
+      </c>
+      <c r="L9" s="2">
+        <v>8</v>
+      </c>
+      <c r="M9" s="4">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5">
+        <v>29503</v>
+      </c>
+      <c r="O9" s="2">
+        <v>28706</v>
+      </c>
+      <c r="P9" s="2">
+        <v>674</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>99</v>
+      </c>
+      <c r="R9" s="2">
+        <v>20</v>
+      </c>
+      <c r="S9" s="3">
+        <v>4</v>
+      </c>
+      <c r="T9" s="1">
+        <v>19589</v>
+      </c>
+      <c r="U9" s="2">
+        <v>19447</v>
+      </c>
+      <c r="V9" s="2">
+        <v>133</v>
+      </c>
+      <c r="W9" s="2">
+        <v>9</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>24588</v>
+      </c>
+      <c r="C10" s="2">
+        <v>23913</v>
+      </c>
+      <c r="D10" s="2">
+        <v>550</v>
+      </c>
+      <c r="E10" s="2">
+        <v>98</v>
+      </c>
+      <c r="F10" s="2">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1">
+        <v>196</v>
+      </c>
+      <c r="I10" s="2">
+        <v>117</v>
+      </c>
+      <c r="J10" s="2">
+        <v>36</v>
+      </c>
+      <c r="K10" s="2">
+        <v>32</v>
+      </c>
+      <c r="L10" s="2">
+        <v>6</v>
+      </c>
+      <c r="M10" s="4">
+        <v>5</v>
+      </c>
+      <c r="N10" s="5">
+        <v>23354</v>
+      </c>
+      <c r="O10" s="2">
+        <v>22760</v>
+      </c>
+      <c r="P10" s="2">
+        <v>512</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>66</v>
+      </c>
+      <c r="R10" s="2">
+        <v>10</v>
+      </c>
+      <c r="S10" s="3">
+        <v>6</v>
+      </c>
+      <c r="T10" s="1">
+        <v>15173</v>
+      </c>
+      <c r="U10" s="2">
+        <v>15066</v>
+      </c>
+      <c r="V10" s="2">
+        <v>102</v>
+      </c>
+      <c r="W10" s="2">
+        <v>5</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25358</v>
+      </c>
+      <c r="C11" s="2">
+        <v>24549</v>
+      </c>
+      <c r="D11" s="2">
+        <v>655</v>
+      </c>
+      <c r="E11" s="2">
+        <v>125</v>
+      </c>
+      <c r="F11" s="2">
+        <v>25</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>150</v>
+      </c>
+      <c r="I11" s="2">
+        <v>59</v>
+      </c>
+      <c r="J11" s="2">
+        <v>58</v>
+      </c>
+      <c r="K11" s="2">
+        <v>27</v>
+      </c>
+      <c r="L11" s="2">
+        <v>5</v>
+      </c>
+      <c r="M11" s="4">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5">
+        <v>24414</v>
+      </c>
+      <c r="O11" s="2">
+        <v>23696</v>
+      </c>
+      <c r="P11" s="2">
+        <v>597</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>98</v>
+      </c>
+      <c r="R11" s="2">
+        <v>20</v>
+      </c>
+      <c r="S11" s="3">
+        <v>3</v>
+      </c>
+      <c r="T11" s="1">
+        <v>18126</v>
+      </c>
+      <c r="U11" s="2">
+        <v>17955</v>
+      </c>
+      <c r="V11" s="2">
+        <v>165</v>
+      </c>
+      <c r="W11" s="2">
+        <v>6</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1">
+        <v>41045</v>
+      </c>
+      <c r="C12" s="2">
+        <v>40001</v>
+      </c>
+      <c r="D12" s="2">
+        <v>830</v>
+      </c>
+      <c r="E12" s="2">
+        <v>176</v>
+      </c>
+      <c r="F12" s="2">
+        <v>31</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7</v>
+      </c>
+      <c r="H12" s="1">
+        <v>728</v>
+      </c>
+      <c r="I12" s="2">
+        <v>573</v>
+      </c>
+      <c r="J12" s="2">
+        <v>62</v>
+      </c>
+      <c r="K12" s="2">
+        <v>68</v>
+      </c>
+      <c r="L12" s="2">
+        <v>19</v>
+      </c>
+      <c r="M12" s="4">
+        <v>6</v>
+      </c>
+      <c r="N12" s="5">
+        <v>39093</v>
+      </c>
+      <c r="O12" s="2">
+        <v>38206</v>
+      </c>
+      <c r="P12" s="2">
+        <v>766</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>108</v>
+      </c>
+      <c r="R12" s="2">
+        <v>12</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>23271</v>
+      </c>
+      <c r="U12" s="2">
+        <v>23096</v>
+      </c>
+      <c r="V12" s="2">
+        <v>163</v>
+      </c>
+      <c r="W12" s="2">
+        <v>11</v>
+      </c>
+      <c r="X12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1">
+        <v>12573</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12275</v>
+      </c>
+      <c r="D13" s="2">
+        <v>241</v>
+      </c>
+      <c r="E13" s="2">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>89</v>
+      </c>
+      <c r="I13" s="2">
         <v>43</v>
       </c>
-      <c r="M8" s="9">
-        <v>14</v>
-      </c>
-      <c r="N8" s="10">
-        <v>130599</v>
-      </c>
-      <c r="O8" s="7">
-        <v>127263</v>
-      </c>
-      <c r="P8" s="7">
-        <v>2838</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>411</v>
-      </c>
-      <c r="R8" s="7">
-        <v>73</v>
-      </c>
-      <c r="S8" s="8">
-        <v>14</v>
-      </c>
-      <c r="T8" s="6">
-        <v>84674</v>
-      </c>
-      <c r="U8" s="7">
-        <v>84023</v>
-      </c>
-      <c r="V8" s="7">
-        <v>617</v>
-      </c>
-      <c r="W8" s="7">
-        <v>33</v>
-      </c>
-      <c r="X8" s="7">
+      <c r="J13" s="2">
+        <v>22</v>
+      </c>
+      <c r="K13" s="2">
+        <v>18</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5</v>
+      </c>
+      <c r="M13" s="4">
         <v>1</v>
       </c>
-      <c r="Y8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="N13" s="5">
+        <v>12236</v>
+      </c>
+      <c r="O13" s="2">
+        <v>11985</v>
+      </c>
+      <c r="P13" s="2">
+        <v>218</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>23</v>
+      </c>
+      <c r="R13" s="2">
+        <v>10</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>8497</v>
+      </c>
+      <c r="U13" s="2">
+        <v>8441</v>
+      </c>
+      <c r="V13" s="2">
+        <v>54</v>
+      </c>
+      <c r="W13" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="6">
-        <v>2433</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2344</v>
-      </c>
-      <c r="D9" s="7">
-        <v>71</v>
-      </c>
-      <c r="E9" s="7">
-        <v>17</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>8</v>
-      </c>
-      <c r="I9" s="7">
-        <v>8</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
-        <v>1999</v>
-      </c>
-      <c r="O9" s="7">
-        <v>1910</v>
-      </c>
-      <c r="P9" s="7">
-        <v>71</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>17</v>
-      </c>
-      <c r="R9" s="7">
-        <v>1</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6">
-        <v>18</v>
-      </c>
-      <c r="U9" s="7">
-        <v>18</v>
-      </c>
-      <c r="V9" s="7">
-        <v>0</v>
-      </c>
-      <c r="W9" s="7">
-        <v>0</v>
-      </c>
-      <c r="X9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="6">
-        <v>30754</v>
-      </c>
-      <c r="C10" s="7">
-        <v>29862</v>
-      </c>
-      <c r="D10" s="7">
-        <v>727</v>
-      </c>
-      <c r="E10" s="7">
-        <v>132</v>
-      </c>
-      <c r="F10" s="7">
-        <v>28</v>
-      </c>
-      <c r="G10" s="8">
-        <v>5</v>
-      </c>
-      <c r="H10" s="6">
-        <v>205</v>
-      </c>
-      <c r="I10" s="7">
-        <v>110</v>
-      </c>
-      <c r="J10" s="7">
-        <v>53</v>
-      </c>
-      <c r="K10" s="7">
-        <v>33</v>
-      </c>
-      <c r="L10" s="7">
-        <v>8</v>
-      </c>
-      <c r="M10" s="9">
-        <v>1</v>
-      </c>
-      <c r="N10" s="10">
-        <v>29503</v>
-      </c>
-      <c r="O10" s="7">
-        <v>28706</v>
-      </c>
-      <c r="P10" s="7">
-        <v>674</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>99</v>
-      </c>
-      <c r="R10" s="7">
-        <v>20</v>
-      </c>
-      <c r="S10" s="8">
-        <v>4</v>
-      </c>
-      <c r="T10" s="6">
-        <v>19589</v>
-      </c>
-      <c r="U10" s="7">
-        <v>19447</v>
-      </c>
-      <c r="V10" s="7">
-        <v>133</v>
-      </c>
-      <c r="W10" s="7">
-        <v>9</v>
-      </c>
-      <c r="X10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="6">
-        <v>24588</v>
-      </c>
-      <c r="C11" s="7">
-        <v>23913</v>
-      </c>
-      <c r="D11" s="7">
-        <v>550</v>
-      </c>
-      <c r="E11" s="7">
-        <v>98</v>
-      </c>
-      <c r="F11" s="7">
-        <v>16</v>
-      </c>
-      <c r="G11" s="8">
-        <v>11</v>
-      </c>
-      <c r="H11" s="6">
-        <v>196</v>
-      </c>
-      <c r="I11" s="7">
-        <v>117</v>
-      </c>
-      <c r="J11" s="7">
-        <v>36</v>
-      </c>
-      <c r="K11" s="7">
-        <v>32</v>
-      </c>
-      <c r="L11" s="7">
-        <v>6</v>
-      </c>
-      <c r="M11" s="9">
-        <v>5</v>
-      </c>
-      <c r="N11" s="10">
-        <v>23354</v>
-      </c>
-      <c r="O11" s="7">
-        <v>22760</v>
-      </c>
-      <c r="P11" s="7">
-        <v>512</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>66</v>
-      </c>
-      <c r="R11" s="7">
-        <v>10</v>
-      </c>
-      <c r="S11" s="8">
-        <v>6</v>
-      </c>
-      <c r="T11" s="6">
-        <v>15173</v>
-      </c>
-      <c r="U11" s="7">
-        <v>15066</v>
-      </c>
-      <c r="V11" s="7">
-        <v>102</v>
-      </c>
-      <c r="W11" s="7">
-        <v>5</v>
-      </c>
-      <c r="X11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="6">
-        <v>25358</v>
-      </c>
-      <c r="C12" s="7">
-        <v>24549</v>
-      </c>
-      <c r="D12" s="7">
-        <v>655</v>
-      </c>
-      <c r="E12" s="7">
-        <v>125</v>
-      </c>
-      <c r="F12" s="7">
-        <v>25</v>
-      </c>
-      <c r="G12" s="8">
-        <v>4</v>
-      </c>
-      <c r="H12" s="6">
-        <v>150</v>
-      </c>
-      <c r="I12" s="7">
-        <v>59</v>
-      </c>
-      <c r="J12" s="7">
-        <v>58</v>
-      </c>
-      <c r="K12" s="7">
-        <v>27</v>
-      </c>
-      <c r="L12" s="7">
-        <v>5</v>
-      </c>
-      <c r="M12" s="9">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10">
-        <v>24414</v>
-      </c>
-      <c r="O12" s="7">
-        <v>23696</v>
-      </c>
-      <c r="P12" s="7">
-        <v>597</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>98</v>
-      </c>
-      <c r="R12" s="7">
-        <v>20</v>
-      </c>
-      <c r="S12" s="8">
-        <v>3</v>
-      </c>
-      <c r="T12" s="6">
-        <v>18126</v>
-      </c>
-      <c r="U12" s="7">
-        <v>17955</v>
-      </c>
-      <c r="V12" s="7">
-        <v>165</v>
-      </c>
-      <c r="W12" s="7">
-        <v>6</v>
-      </c>
-      <c r="X12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="6">
-        <v>41045</v>
-      </c>
-      <c r="C13" s="7">
-        <v>40001</v>
-      </c>
-      <c r="D13" s="7">
-        <v>830</v>
-      </c>
-      <c r="E13" s="7">
-        <v>176</v>
-      </c>
-      <c r="F13" s="7">
-        <v>31</v>
-      </c>
-      <c r="G13" s="8">
-        <v>7</v>
-      </c>
-      <c r="H13" s="6">
-        <v>728</v>
-      </c>
-      <c r="I13" s="7">
-        <v>573</v>
-      </c>
-      <c r="J13" s="7">
-        <v>62</v>
-      </c>
-      <c r="K13" s="7">
-        <v>68</v>
-      </c>
-      <c r="L13" s="7">
-        <v>19</v>
-      </c>
-      <c r="M13" s="9">
-        <v>6</v>
-      </c>
-      <c r="N13" s="10">
-        <v>39093</v>
-      </c>
-      <c r="O13" s="7">
-        <v>38206</v>
-      </c>
-      <c r="P13" s="7">
-        <v>766</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>108</v>
-      </c>
-      <c r="R13" s="7">
-        <v>12</v>
-      </c>
-      <c r="S13" s="8">
-        <v>1</v>
-      </c>
-      <c r="T13" s="6">
-        <v>23271</v>
-      </c>
-      <c r="U13" s="7">
-        <v>23096</v>
-      </c>
-      <c r="V13" s="7">
-        <v>163</v>
-      </c>
-      <c r="W13" s="7">
-        <v>11</v>
-      </c>
-      <c r="X13" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="6">
-        <v>12573</v>
-      </c>
-      <c r="C14" s="7">
-        <v>12275</v>
-      </c>
-      <c r="D14" s="7">
-        <v>241</v>
-      </c>
-      <c r="E14" s="7">
-        <v>41</v>
-      </c>
-      <c r="F14" s="7">
-        <v>15</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6">
-        <v>89</v>
-      </c>
-      <c r="I14" s="7">
-        <v>43</v>
-      </c>
-      <c r="J14" s="7">
-        <v>22</v>
-      </c>
-      <c r="K14" s="7">
-        <v>18</v>
-      </c>
-      <c r="L14" s="7">
-        <v>5</v>
-      </c>
-      <c r="M14" s="9">
-        <v>1</v>
-      </c>
-      <c r="N14" s="10">
-        <v>12236</v>
-      </c>
-      <c r="O14" s="7">
-        <v>11985</v>
-      </c>
-      <c r="P14" s="7">
-        <v>218</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>23</v>
-      </c>
-      <c r="R14" s="7">
-        <v>10</v>
-      </c>
-      <c r="S14" s="8">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6">
-        <v>8497</v>
-      </c>
-      <c r="U14" s="7">
-        <v>8441</v>
-      </c>
-      <c r="V14" s="7">
-        <v>54</v>
-      </c>
-      <c r="W14" s="7">
-        <v>2</v>
-      </c>
-      <c r="X14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9">
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="Q2:Q6"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="G2:G6"/>
+    <mergeCell ref="H2:H6"/>
+    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="J2:J6"/>
+    <mergeCell ref="K2:K6"/>
+    <mergeCell ref="L2:L6"/>
+    <mergeCell ref="M2:M6"/>
+    <mergeCell ref="N2:N6"/>
+    <mergeCell ref="O2:O6"/>
+    <mergeCell ref="P2:P6"/>
     <mergeCell ref="R2:R6"/>
     <mergeCell ref="S2:S6"/>
     <mergeCell ref="T2:Y2"/>
@@ -1697,25 +1618,6 @@
     <mergeCell ref="W3:W6"/>
     <mergeCell ref="X3:X6"/>
     <mergeCell ref="Y3:Y6"/>
-    <mergeCell ref="L2:L6"/>
-    <mergeCell ref="M2:M6"/>
-    <mergeCell ref="N2:N6"/>
-    <mergeCell ref="O2:O6"/>
-    <mergeCell ref="P2:P6"/>
-    <mergeCell ref="Q2:Q6"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="G2:G6"/>
-    <mergeCell ref="H2:H6"/>
-    <mergeCell ref="I2:I6"/>
-    <mergeCell ref="J2:J6"/>
-    <mergeCell ref="K2:K6"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="E2:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CSV/regon.xlsx
+++ b/Data/CSV/regon.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Documents\GitHub\MobilityPatterns\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Documents\GitHub\MobilityPatterns\data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C61015-327A-4837-AFB8-50DCF48EC0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C7AD5D-B7DF-4260-9343-BFC6BC8FB5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{178E5E3B-8F57-4D60-BDFA-D04E6B9AA60C}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,14 +107,6 @@
     <font>
       <b/>
       <sz val="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="238"/>
@@ -210,7 +202,189 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thick">
         <color indexed="64"/>
       </top>
@@ -221,67 +395,9 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -290,128 +406,10 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
@@ -423,70 +421,70 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -830,227 +828,227 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="19" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="19" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="22"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="15"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="17"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="14" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="V3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="W3" s="10" t="s">
+      <c r="W3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="X3" s="10" t="s">
+      <c r="X3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="17" t="s">
+      <c r="Y3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="17"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="18"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="17"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="18"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="18"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="19"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="1">
@@ -1127,7 +1125,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="1">
@@ -1204,7 +1202,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="1">
@@ -1281,7 +1279,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -1358,7 +1356,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="1">
@@ -1435,7 +1433,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="1">
@@ -1512,7 +1510,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="1">
@@ -1589,7 +1587,20 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="T3:T6"/>
+    <mergeCell ref="U3:U6"/>
+    <mergeCell ref="V3:V6"/>
+    <mergeCell ref="W3:W6"/>
+    <mergeCell ref="X3:X6"/>
+    <mergeCell ref="Y3:Y6"/>
+    <mergeCell ref="N2:N6"/>
+    <mergeCell ref="O2:O6"/>
+    <mergeCell ref="P2:P6"/>
+    <mergeCell ref="R2:R6"/>
+    <mergeCell ref="S2:S6"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="N1:Y1"/>
@@ -1606,18 +1617,6 @@
     <mergeCell ref="K2:K6"/>
     <mergeCell ref="L2:L6"/>
     <mergeCell ref="M2:M6"/>
-    <mergeCell ref="N2:N6"/>
-    <mergeCell ref="O2:O6"/>
-    <mergeCell ref="P2:P6"/>
-    <mergeCell ref="R2:R6"/>
-    <mergeCell ref="S2:S6"/>
-    <mergeCell ref="T2:Y2"/>
-    <mergeCell ref="T3:T6"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="V3:V6"/>
-    <mergeCell ref="W3:W6"/>
-    <mergeCell ref="X3:X6"/>
-    <mergeCell ref="Y3:Y6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CSV/regon.xlsx
+++ b/Data/CSV/regon.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Documents\GitHub\MobilityPatterns\data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wozni\OneDrive\Pulpit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C7AD5D-B7DF-4260-9343-BFC6BC8FB5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD4D93B1-42D1-4BFB-8382-B2AECE2BAE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{178E5E3B-8F57-4D60-BDFA-D04E6B9AA60C}"/>
   </bookViews>
@@ -36,7 +36,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">podregion M. POZNAŃ               </t>
+  </si>
   <si>
     <t>powiat M. POZNAŃ</t>
   </si>
@@ -96,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +110,14 @@
     <font>
       <b/>
       <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="238"/>
@@ -202,6 +213,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -262,6 +284,15 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -322,6 +353,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -373,43 +415,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
@@ -419,73 +424,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,234 +844,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401DBD47-1B97-4A32-92C7-8196E923716B}">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="7" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="10"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="14"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="E2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="13" t="s">
+      <c r="G2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="J2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="K2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="L2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="13" t="s">
+      <c r="M2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="O2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="P2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="Q2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="R2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="S2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="17"/>
+      <c r="T2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="19"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="U3" s="13" t="s">
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="U3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="V3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="W3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="18" t="s">
+      <c r="X3" s="17" t="s">
         <v>16</v>
+      </c>
+      <c r="Y3" s="20" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="18"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="20"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="18"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="20"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="19"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="25"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="1">
@@ -1125,470 +1148,548 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="6">
+        <v>136751</v>
+      </c>
+      <c r="C8" s="7">
+        <v>132944</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3074</v>
+      </c>
+      <c r="E8" s="7">
+        <v>589</v>
+      </c>
+      <c r="F8" s="7">
+        <v>116</v>
+      </c>
+      <c r="G8" s="8">
+        <v>28</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1376</v>
+      </c>
+      <c r="I8" s="7">
+        <v>910</v>
+      </c>
+      <c r="J8" s="7">
+        <v>231</v>
+      </c>
+      <c r="K8" s="7">
+        <v>178</v>
+      </c>
+      <c r="L8" s="7">
+        <v>43</v>
+      </c>
+      <c r="M8" s="9">
+        <v>14</v>
+      </c>
+      <c r="N8" s="10">
+        <v>130599</v>
+      </c>
+      <c r="O8" s="7">
+        <v>127263</v>
+      </c>
+      <c r="P8" s="7">
+        <v>2838</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>411</v>
+      </c>
+      <c r="R8" s="7">
+        <v>73</v>
+      </c>
+      <c r="S8" s="8">
+        <v>14</v>
+      </c>
+      <c r="T8" s="6">
+        <v>84674</v>
+      </c>
+      <c r="U8" s="7">
+        <v>84023</v>
+      </c>
+      <c r="V8" s="7">
+        <v>617</v>
+      </c>
+      <c r="W8" s="7">
+        <v>33</v>
+      </c>
+      <c r="X8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6">
         <v>2433</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C9" s="7">
         <v>2344</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="7">
         <v>71</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E9" s="7">
         <v>17</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
         <v>8</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I9" s="7">
         <v>8</v>
       </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
         <v>1999</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O9" s="7">
         <v>1910</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P9" s="7">
         <v>71</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q9" s="7">
         <v>17</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R9" s="7">
         <v>1</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
+      <c r="S9" s="8">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6">
         <v>18</v>
       </c>
-      <c r="U8" s="2">
+      <c r="U9" s="7">
         <v>18</v>
       </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4">
+      <c r="V9" s="7">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="10" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
+        <v>30754</v>
+      </c>
+      <c r="C10" s="7">
+        <v>29862</v>
+      </c>
+      <c r="D10" s="7">
+        <v>727</v>
+      </c>
+      <c r="E10" s="7">
+        <v>132</v>
+      </c>
+      <c r="F10" s="7">
+        <v>28</v>
+      </c>
+      <c r="G10" s="8">
+        <v>5</v>
+      </c>
+      <c r="H10" s="6">
+        <v>205</v>
+      </c>
+      <c r="I10" s="7">
+        <v>110</v>
+      </c>
+      <c r="J10" s="7">
+        <v>53</v>
+      </c>
+      <c r="K10" s="7">
+        <v>33</v>
+      </c>
+      <c r="L10" s="7">
+        <v>8</v>
+      </c>
+      <c r="M10" s="9">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10">
+        <v>29503</v>
+      </c>
+      <c r="O10" s="7">
+        <v>28706</v>
+      </c>
+      <c r="P10" s="7">
+        <v>674</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>99</v>
+      </c>
+      <c r="R10" s="7">
+        <v>20</v>
+      </c>
+      <c r="S10" s="8">
+        <v>4</v>
+      </c>
+      <c r="T10" s="6">
+        <v>19589</v>
+      </c>
+      <c r="U10" s="7">
+        <v>19447</v>
+      </c>
+      <c r="V10" s="7">
+        <v>133</v>
+      </c>
+      <c r="W10" s="7">
+        <v>9</v>
+      </c>
+      <c r="X10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6">
+        <v>24588</v>
+      </c>
+      <c r="C11" s="7">
+        <v>23913</v>
+      </c>
+      <c r="D11" s="7">
+        <v>550</v>
+      </c>
+      <c r="E11" s="7">
+        <v>98</v>
+      </c>
+      <c r="F11" s="7">
+        <v>16</v>
+      </c>
+      <c r="G11" s="8">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6">
+        <v>196</v>
+      </c>
+      <c r="I11" s="7">
+        <v>117</v>
+      </c>
+      <c r="J11" s="7">
+        <v>36</v>
+      </c>
+      <c r="K11" s="7">
+        <v>32</v>
+      </c>
+      <c r="L11" s="7">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9">
+        <v>5</v>
+      </c>
+      <c r="N11" s="10">
+        <v>23354</v>
+      </c>
+      <c r="O11" s="7">
+        <v>22760</v>
+      </c>
+      <c r="P11" s="7">
+        <v>512</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>66</v>
+      </c>
+      <c r="R11" s="7">
+        <v>10</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="6">
+        <v>15173</v>
+      </c>
+      <c r="U11" s="7">
+        <v>15066</v>
+      </c>
+      <c r="V11" s="7">
+        <v>102</v>
+      </c>
+      <c r="W11" s="7">
+        <v>5</v>
+      </c>
+      <c r="X11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6">
+        <v>25358</v>
+      </c>
+      <c r="C12" s="7">
+        <v>24549</v>
+      </c>
+      <c r="D12" s="7">
+        <v>655</v>
+      </c>
+      <c r="E12" s="7">
+        <v>125</v>
+      </c>
+      <c r="F12" s="7">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6">
+        <v>150</v>
+      </c>
+      <c r="I12" s="7">
+        <v>59</v>
+      </c>
+      <c r="J12" s="7">
+        <v>58</v>
+      </c>
+      <c r="K12" s="7">
+        <v>27</v>
+      </c>
+      <c r="L12" s="7">
+        <v>5</v>
+      </c>
+      <c r="M12" s="9">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>24414</v>
+      </c>
+      <c r="O12" s="7">
+        <v>23696</v>
+      </c>
+      <c r="P12" s="7">
+        <v>597</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>98</v>
+      </c>
+      <c r="R12" s="7">
+        <v>20</v>
+      </c>
+      <c r="S12" s="8">
+        <v>3</v>
+      </c>
+      <c r="T12" s="6">
+        <v>18126</v>
+      </c>
+      <c r="U12" s="7">
+        <v>17955</v>
+      </c>
+      <c r="V12" s="7">
+        <v>165</v>
+      </c>
+      <c r="W12" s="7">
+        <v>6</v>
+      </c>
+      <c r="X12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6">
+        <v>41045</v>
+      </c>
+      <c r="C13" s="7">
+        <v>40001</v>
+      </c>
+      <c r="D13" s="7">
+        <v>830</v>
+      </c>
+      <c r="E13" s="7">
+        <v>176</v>
+      </c>
+      <c r="F13" s="7">
+        <v>31</v>
+      </c>
+      <c r="G13" s="8">
+        <v>7</v>
+      </c>
+      <c r="H13" s="6">
+        <v>728</v>
+      </c>
+      <c r="I13" s="7">
+        <v>573</v>
+      </c>
+      <c r="J13" s="7">
+        <v>62</v>
+      </c>
+      <c r="K13" s="7">
+        <v>68</v>
+      </c>
+      <c r="L13" s="7">
+        <v>19</v>
+      </c>
+      <c r="M13" s="9">
+        <v>6</v>
+      </c>
+      <c r="N13" s="10">
+        <v>39093</v>
+      </c>
+      <c r="O13" s="7">
+        <v>38206</v>
+      </c>
+      <c r="P13" s="7">
+        <v>766</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>108</v>
+      </c>
+      <c r="R13" s="7">
+        <v>12</v>
+      </c>
+      <c r="S13" s="8">
+        <v>1</v>
+      </c>
+      <c r="T13" s="6">
+        <v>23271</v>
+      </c>
+      <c r="U13" s="7">
+        <v>23096</v>
+      </c>
+      <c r="V13" s="7">
+        <v>163</v>
+      </c>
+      <c r="W13" s="7">
+        <v>11</v>
+      </c>
+      <c r="X13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6">
+        <v>12573</v>
+      </c>
+      <c r="C14" s="7">
+        <v>12275</v>
+      </c>
+      <c r="D14" s="7">
+        <v>241</v>
+      </c>
+      <c r="E14" s="7">
+        <v>41</v>
+      </c>
+      <c r="F14" s="7">
+        <v>15</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <v>89</v>
+      </c>
+      <c r="I14" s="7">
+        <v>43</v>
+      </c>
+      <c r="J14" s="7">
+        <v>22</v>
+      </c>
+      <c r="K14" s="7">
+        <v>18</v>
+      </c>
+      <c r="L14" s="7">
+        <v>5</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>12236</v>
+      </c>
+      <c r="O14" s="7">
+        <v>11985</v>
+      </c>
+      <c r="P14" s="7">
+        <v>218</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>23</v>
+      </c>
+      <c r="R14" s="7">
+        <v>10</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6">
+        <v>8497</v>
+      </c>
+      <c r="U14" s="7">
+        <v>8441</v>
+      </c>
+      <c r="V14" s="7">
+        <v>54</v>
+      </c>
+      <c r="W14" s="7">
         <v>2</v>
       </c>
-      <c r="B9" s="1">
-        <v>30754</v>
-      </c>
-      <c r="C9" s="2">
-        <v>29862</v>
-      </c>
-      <c r="D9" s="2">
-        <v>727</v>
-      </c>
-      <c r="E9" s="2">
-        <v>132</v>
-      </c>
-      <c r="F9" s="2">
-        <v>28</v>
-      </c>
-      <c r="G9" s="3">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1">
-        <v>205</v>
-      </c>
-      <c r="I9" s="2">
-        <v>110</v>
-      </c>
-      <c r="J9" s="2">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2">
-        <v>33</v>
-      </c>
-      <c r="L9" s="2">
-        <v>8</v>
-      </c>
-      <c r="M9" s="4">
-        <v>1</v>
-      </c>
-      <c r="N9" s="5">
-        <v>29503</v>
-      </c>
-      <c r="O9" s="2">
-        <v>28706</v>
-      </c>
-      <c r="P9" s="2">
-        <v>674</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>99</v>
-      </c>
-      <c r="R9" s="2">
-        <v>20</v>
-      </c>
-      <c r="S9" s="3">
-        <v>4</v>
-      </c>
-      <c r="T9" s="1">
-        <v>19589</v>
-      </c>
-      <c r="U9" s="2">
-        <v>19447</v>
-      </c>
-      <c r="V9" s="2">
-        <v>133</v>
-      </c>
-      <c r="W9" s="2">
-        <v>9</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1">
-        <v>24588</v>
-      </c>
-      <c r="C10" s="2">
-        <v>23913</v>
-      </c>
-      <c r="D10" s="2">
-        <v>550</v>
-      </c>
-      <c r="E10" s="2">
-        <v>98</v>
-      </c>
-      <c r="F10" s="2">
-        <v>16</v>
-      </c>
-      <c r="G10" s="3">
-        <v>11</v>
-      </c>
-      <c r="H10" s="1">
-        <v>196</v>
-      </c>
-      <c r="I10" s="2">
-        <v>117</v>
-      </c>
-      <c r="J10" s="2">
-        <v>36</v>
-      </c>
-      <c r="K10" s="2">
-        <v>32</v>
-      </c>
-      <c r="L10" s="2">
-        <v>6</v>
-      </c>
-      <c r="M10" s="4">
-        <v>5</v>
-      </c>
-      <c r="N10" s="5">
-        <v>23354</v>
-      </c>
-      <c r="O10" s="2">
-        <v>22760</v>
-      </c>
-      <c r="P10" s="2">
-        <v>512</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>66</v>
-      </c>
-      <c r="R10" s="2">
-        <v>10</v>
-      </c>
-      <c r="S10" s="3">
-        <v>6</v>
-      </c>
-      <c r="T10" s="1">
-        <v>15173</v>
-      </c>
-      <c r="U10" s="2">
-        <v>15066</v>
-      </c>
-      <c r="V10" s="2">
-        <v>102</v>
-      </c>
-      <c r="W10" s="2">
-        <v>5</v>
-      </c>
-      <c r="X10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
-        <v>25358</v>
-      </c>
-      <c r="C11" s="2">
-        <v>24549</v>
-      </c>
-      <c r="D11" s="2">
-        <v>655</v>
-      </c>
-      <c r="E11" s="2">
-        <v>125</v>
-      </c>
-      <c r="F11" s="2">
-        <v>25</v>
-      </c>
-      <c r="G11" s="3">
-        <v>4</v>
-      </c>
-      <c r="H11" s="1">
-        <v>150</v>
-      </c>
-      <c r="I11" s="2">
-        <v>59</v>
-      </c>
-      <c r="J11" s="2">
-        <v>58</v>
-      </c>
-      <c r="K11" s="2">
-        <v>27</v>
-      </c>
-      <c r="L11" s="2">
-        <v>5</v>
-      </c>
-      <c r="M11" s="4">
-        <v>1</v>
-      </c>
-      <c r="N11" s="5">
-        <v>24414</v>
-      </c>
-      <c r="O11" s="2">
-        <v>23696</v>
-      </c>
-      <c r="P11" s="2">
-        <v>597</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>98</v>
-      </c>
-      <c r="R11" s="2">
-        <v>20</v>
-      </c>
-      <c r="S11" s="3">
-        <v>3</v>
-      </c>
-      <c r="T11" s="1">
-        <v>18126</v>
-      </c>
-      <c r="U11" s="2">
-        <v>17955</v>
-      </c>
-      <c r="V11" s="2">
-        <v>165</v>
-      </c>
-      <c r="W11" s="2">
-        <v>6</v>
-      </c>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1">
-        <v>41045</v>
-      </c>
-      <c r="C12" s="2">
-        <v>40001</v>
-      </c>
-      <c r="D12" s="2">
-        <v>830</v>
-      </c>
-      <c r="E12" s="2">
-        <v>176</v>
-      </c>
-      <c r="F12" s="2">
-        <v>31</v>
-      </c>
-      <c r="G12" s="3">
-        <v>7</v>
-      </c>
-      <c r="H12" s="1">
-        <v>728</v>
-      </c>
-      <c r="I12" s="2">
-        <v>573</v>
-      </c>
-      <c r="J12" s="2">
-        <v>62</v>
-      </c>
-      <c r="K12" s="2">
-        <v>68</v>
-      </c>
-      <c r="L12" s="2">
-        <v>19</v>
-      </c>
-      <c r="M12" s="4">
-        <v>6</v>
-      </c>
-      <c r="N12" s="5">
-        <v>39093</v>
-      </c>
-      <c r="O12" s="2">
-        <v>38206</v>
-      </c>
-      <c r="P12" s="2">
-        <v>766</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>108</v>
-      </c>
-      <c r="R12" s="2">
-        <v>12</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1">
-        <v>23271</v>
-      </c>
-      <c r="U12" s="2">
-        <v>23096</v>
-      </c>
-      <c r="V12" s="2">
-        <v>163</v>
-      </c>
-      <c r="W12" s="2">
-        <v>11</v>
-      </c>
-      <c r="X12" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1">
-        <v>12573</v>
-      </c>
-      <c r="C13" s="2">
-        <v>12275</v>
-      </c>
-      <c r="D13" s="2">
-        <v>241</v>
-      </c>
-      <c r="E13" s="2">
-        <v>41</v>
-      </c>
-      <c r="F13" s="2">
-        <v>15</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>89</v>
-      </c>
-      <c r="I13" s="2">
-        <v>43</v>
-      </c>
-      <c r="J13" s="2">
-        <v>22</v>
-      </c>
-      <c r="K13" s="2">
-        <v>18</v>
-      </c>
-      <c r="L13" s="2">
-        <v>5</v>
-      </c>
-      <c r="M13" s="4">
-        <v>1</v>
-      </c>
-      <c r="N13" s="5">
-        <v>12236</v>
-      </c>
-      <c r="O13" s="2">
-        <v>11985</v>
-      </c>
-      <c r="P13" s="2">
-        <v>218</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>23</v>
-      </c>
-      <c r="R13" s="2">
-        <v>10</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>8497</v>
-      </c>
-      <c r="U13" s="2">
-        <v>8441</v>
-      </c>
-      <c r="V13" s="2">
-        <v>54</v>
-      </c>
-      <c r="W13" s="2">
-        <v>2</v>
-      </c>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4">
+      <c r="X14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A1:A6"/>
+  <mergeCells count="28">
+    <mergeCell ref="R2:R6"/>
+    <mergeCell ref="S2:S6"/>
     <mergeCell ref="T2:Y2"/>
     <mergeCell ref="T3:T6"/>
     <mergeCell ref="U3:U6"/>
@@ -1596,11 +1697,18 @@
     <mergeCell ref="W3:W6"/>
     <mergeCell ref="X3:X6"/>
     <mergeCell ref="Y3:Y6"/>
+    <mergeCell ref="L2:L6"/>
+    <mergeCell ref="M2:M6"/>
     <mergeCell ref="N2:N6"/>
     <mergeCell ref="O2:O6"/>
     <mergeCell ref="P2:P6"/>
-    <mergeCell ref="R2:R6"/>
-    <mergeCell ref="S2:S6"/>
+    <mergeCell ref="Q2:Q6"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="G2:G6"/>
+    <mergeCell ref="H2:H6"/>
+    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="J2:J6"/>
+    <mergeCell ref="K2:K6"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="N1:Y1"/>
@@ -1608,15 +1716,6 @@
     <mergeCell ref="C2:C6"/>
     <mergeCell ref="D2:D6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="Q2:Q6"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="G2:G6"/>
-    <mergeCell ref="H2:H6"/>
-    <mergeCell ref="I2:I6"/>
-    <mergeCell ref="J2:J6"/>
-    <mergeCell ref="K2:K6"/>
-    <mergeCell ref="L2:L6"/>
-    <mergeCell ref="M2:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
